--- a/documents_new/4 WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents_new/4 WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D297B0ED-4CF3-4C53-84B7-3A0294364E23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0351B282-BF78-4112-8318-2A5219313D68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="31110" windowHeight="13335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -698,6 +698,21 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -712,21 +727,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1086,25 +1086,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="38.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="23"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
@@ -1113,9 +1113,9 @@
       <c r="B5" s="11">
         <v>1411</v>
       </c>
-      <c r="C5" s="23" t="str">
+      <c r="C5" s="28" t="str">
         <f ca="1">"["&amp;B5&amp;"]-["&amp;B6&amp;"]-["&amp;B7&amp;"]-["&amp;B8&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
-        <v>[1411]-[L]-[254658]-[이00]-[0417]-[0147]</v>
+        <v>[1411]-[L]-[254658]-[이00]-[0417]-[0757]</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1125,7 +1125,7 @@
       <c r="B6" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="24"/>
+      <c r="C6" s="29"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
@@ -1134,7 +1134,7 @@
       <c r="B7" s="11">
         <v>254658</v>
       </c>
-      <c r="C7" s="24"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
@@ -1143,14 +1143,14 @@
       <c r="B8" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="24"/>
+      <c r="C8" s="29"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="27"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="23"/>
     </row>
     <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
@@ -1159,15 +1159,15 @@
       <c r="B11" s="13">
         <v>12</v>
       </c>
-      <c r="C11" s="20" t="str">
+      <c r="C11" s="25" t="str">
         <f ca="1">"[A]
-* 긴급도:"&amp;IF(B11=10,"🔴",IF(B11=4,"🟠",IF(B11=12,"🟢","")))&amp;"["&amp;B11&amp;"]"&amp;IF($C$5="","", "
-* CaseID:"&amp;$C$5&amp;"
+* 긴급도 : "&amp;IF(B11=10,"🔴",IF(B11=4,"🟠",IF(B11=12,"🟢","")))&amp;"["&amp;B11&amp;"]"&amp;IF($C$5="","", "
+* CaseID : "&amp;$C$5&amp;"
 * 요청사항 : 
 "&amp;B12)</f>
         <v xml:space="preserve">[A]
-* 긴급도:🟢[12]
-* CaseID:[1411]-[L]-[254658]-[이00]-[0417]-[0147]
+* 긴급도 : 🟢[12]
+* CaseID : [1411]-[L]-[254658]-[이00]-[0417]-[0757]
 * 요청사항 : 
 응급실에서 입실하셨습니다. </v>
       </c>
@@ -1179,14 +1179,14 @@
       <c r="B12" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="27"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="27"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
@@ -1199,11 +1199,11 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="23"/>
     </row>
     <row r="18" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
@@ -1212,17 +1212,17 @@
       <c r="B18" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="20" t="str">
+      <c r="C18" s="25" t="str">
         <f ca="1">IF($C$5="","", "[A][야간이음기록]
 * CaseID : "&amp;$C$5&amp;"
-* 상황:"&amp;B18&amp;"
-* 조치:"&amp;B19&amp;"
-* [D]"&amp;B20)</f>
+* 상황 : "&amp;B18&amp;"
+* 조치 : "&amp;B19&amp;"
+* [D]현재상태 : "&amp;B20)</f>
         <v>[A][야간이음기록]
-* CaseID : [1411]-[L]-[254658]-[이00]-[0417]-[0147]
-* 상황:밤에 낙상함
-* 조치:환자 제위치
-* [D]양호</v>
+* CaseID : [1411]-[L]-[254658]-[이00]-[0417]-[0757]
+* 상황 : 밤에 낙상함
+* 조치 : 환자 제위치
+* [D]현재상태 : 양호</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1232,7 +1232,7 @@
       <c r="B19" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="26"/>
     </row>
     <row r="20" spans="1:3" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
@@ -1241,7 +1241,7 @@
       <c r="B20" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="9">
